--- a/planejamento/plano-capacidades.xlsx
+++ b/planejamento/plano-capacidades.xlsx
@@ -22,8 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -129,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,10 +146,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -160,10 +161,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,10 +176,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,10 +191,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,7 +206,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -215,7 +216,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -223,64 +224,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -780,7 +736,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Estatística para DS</t>
+          <t>Statistics for Data Science</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -799,25 +755,25 @@
       <c r="F5" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="40" t="n">
+      <c r="G5" s="7" t="n">
         <v>46296</v>
       </c>
       <c r="H5" s="4">
         <f>ROUNDUP(E5*IF(D5="Profundo",Premissas!$B$4,Premissas!$B$5)/F5,0)</f>
         <v/>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="8">
         <f>G5+H5*7</f>
         <v/>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Livro: Practical Statistics for Data Scientists, 2ª ed. (Bruce, Bruce &amp; Gedeck)</t>
+          <t>Book: Practical Statistics for Data Scientists, 2nd ed. (Bruce, Bruce &amp; Gedeck)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Livro: Estatística Básica (Morettin &amp; Bussab)</t>
+          <t>Book: OpenIntro Statistics, 4th ed. (Diez, Çetinkaya-Rundel &amp; Barr), free at openintro.org</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -839,7 +795,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Lógica de programação e bibliotecas Python para DS</t>
+          <t>Programming Logic and Python Libraries for Data Science</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -858,25 +814,25 @@
       <c r="F6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="40" t="n">
+      <c r="G6" s="7" t="n">
         <v>46296</v>
       </c>
       <c r="H6" s="4">
         <f>ROUNDUP(E6*IF(D6="Profundo",Premissas!$B$4,Premissas!$B$5)/F6,0)</f>
         <v/>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="8">
         <f>G6+H6*7</f>
         <v/>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Livro: Python for Data Analysis, 3ª ed. (Wes McKinney), grátis em wesmckinney.com/book</t>
+          <t>Book: Python for Data Analysis, 3rd ed. (Wes McKinney), free at wesmckinney.com/book</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Repositório: github.com/jakevdp/PythonDataScienceHandbook</t>
+          <t>Repository: github.com/jakevdp/PythonDataScienceHandbook</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -898,7 +854,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SQL / modelagem de dados</t>
+          <t>SQL / Data Modeling</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -917,25 +873,25 @@
       <c r="F7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="40" t="n">
+      <c r="G7" s="7" t="n">
         <v>46296</v>
       </c>
       <c r="H7" s="4">
         <f>ROUNDUP(E7*IF(D7="Profundo",Premissas!$B$4,Premissas!$B$5)/F7,0)</f>
         <v/>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="8">
         <f>G7+H7*7</f>
         <v/>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Livro: Learning SQL, 3ª ed. (Alan Beaulieu)</t>
+          <t>Book: Learning SQL, 3rd ed. (Alan Beaulieu)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Livro: The Data Warehouse Toolkit, 3ª ed. (Kimball &amp; Ross)</t>
+          <t>Book: The Data Warehouse Toolkit, 3rd ed. (Kimball &amp; Ross)</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -957,7 +913,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Git conceitual</t>
+          <t>Git (Conceptual)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -976,20 +932,20 @@
       <c r="F8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="40" t="n">
+      <c r="G8" s="7" t="n">
         <v>46296</v>
       </c>
       <c r="H8" s="4">
         <f>ROUNDUP(E8*IF(D8="Profundo",Premissas!$B$4,Premissas!$B$5)/F8,0)</f>
         <v/>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="8">
         <f>G8+H8*7</f>
         <v/>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Livro: Pro Git, 2ª ed. (Chacon &amp; Straub), grátis em git-scm.com/book — capítulos 1–3 e 10</t>
+          <t>Book: Pro Git, 2nd ed. (Chacon &amp; Straub), free at git-scm.com/book — chapters 1–3 and 10</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1016,7 +972,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Engenharia de prompt / harness / spec</t>
+          <t>Prompt Engineering / Harness / Spec</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1035,25 +991,25 @@
       <c r="F9" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="40" t="n">
+      <c r="G9" s="7" t="n">
         <v>46332</v>
       </c>
       <c r="H9" s="4">
         <f>ROUNDUP(E9*IF(D9="Profundo",Premissas!$B$4,Premissas!$B$5)/F9,0)</f>
         <v/>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="8">
         <f>G9+H9*7</f>
         <v/>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Repositório: github.com/anthropics/prompt-eng-interactive-tutorial</t>
+          <t>Repository: github.com/anthropics/prompt-eng-interactive-tutorial</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Artigo: Building effective agents (Anthropic); documentação da Anthropic sobre prompts e agentes</t>
+          <t>Article: Building effective agents (Anthropic); Docs: Anthropic documentation on prompting and agents</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -1075,7 +1031,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Matemática para DS</t>
+          <t>Mathematics for Data Science</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1094,30 +1050,30 @@
       <c r="F10" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="12" t="n">
         <v>46391</v>
       </c>
       <c r="H10" s="9">
         <f>ROUNDUP(E10*IF(D10="Profundo",Premissas!$B$4,Premissas!$B$5)/F10,0)</f>
         <v/>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="13">
         <f>G10+H10*7</f>
         <v/>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Livro: Mathematics for Machine Learning (Deisenroth, Faisal &amp; Ong), grátis em mml-book.github.io</t>
+          <t>Book: Mathematics for Machine Learning (Deisenroth, Faisal &amp; Ong), free at mml-book.github.io</t>
         </is>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>Curso: Essence of Linear Algebra (3Blue1Brown)</t>
+          <t>Course: Essence of Linear Algebra (3Blue1Brown)</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>Estatística para DS</t>
+          <t>Statistics for Data Science</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
@@ -1134,7 +1090,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>EDA avançada</t>
+          <t>Advanced EDA</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1153,30 +1109,30 @@
       <c r="F11" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="42" t="n">
+      <c r="G11" s="12" t="n">
         <v>46391</v>
       </c>
       <c r="H11" s="9">
         <f>ROUNDUP(E11*IF(D11="Profundo",Premissas!$B$4,Premissas!$B$5)/F11,0)</f>
         <v/>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="13">
         <f>G11+H11*7</f>
         <v/>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Livro: Feature Engineering and Selection (Kuhn &amp; Johnson), grátis em feat.engineering</t>
+          <t>Book: Feature Engineering and Selection (Kuhn &amp; Johnson), free at feat.engineering</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>Repositório: github.com/jakevdp/PythonDataScienceHandbook; as suas bases</t>
+          <t>Repository: github.com/jakevdp/PythonDataScienceHandbook; My own datasets</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>Estatística; Python para DS</t>
+          <t>Statistics; Python for Data Science</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
@@ -1193,7 +1149,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Visualização de dados</t>
+          <t>Data Visualization</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1212,30 +1168,30 @@
       <c r="F12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="42" t="n">
+      <c r="G12" s="12" t="n">
         <v>46391</v>
       </c>
       <c r="H12" s="9">
         <f>ROUNDUP(E12*IF(D12="Profundo",Premissas!$B$4,Premissas!$B$5)/F12,0)</f>
         <v/>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="13">
         <f>G12+H12*7</f>
         <v/>
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Livro: Fundamentals of Data Visualization (Claus Wilke), grátis em clauswilke.com/dataviz</t>
+          <t>Book: Fundamentals of Data Visualization (Claus Wilke), free at clauswilke.com/dataviz</t>
         </is>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>Documentação: matplotlib e seaborn</t>
+          <t>Docs: matplotlib and seaborn</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>Python para DS</t>
+          <t>Python for Data Science</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
@@ -1252,7 +1208,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Storytelling</t>
+          <t>Data Storytelling</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1271,30 +1227,30 @@
       <c r="F13" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="42" t="n">
+      <c r="G13" s="12" t="n">
         <v>46447</v>
       </c>
       <c r="H13" s="9">
         <f>ROUNDUP(E13*IF(D13="Profundo",Premissas!$B$4,Premissas!$B$5)/F13,0)</f>
         <v/>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="13">
         <f>G13+H13*7</f>
         <v/>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Livro: Storytelling with Data (Cole Nussbaumer Knaflic)</t>
+          <t>Book: Storytelling with Data (Cole Nussbaumer Knaflic)</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>Livro: Storytelling with Data: Let's Practice! (Knaflic)</t>
+          <t>Book: Storytelling with Data: Let's Practice! (Knaflic)</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>Visualização de dados</t>
+          <t>Data Visualization</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
@@ -1311,7 +1267,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Engenharia de IA</t>
+          <t>AI Engineering</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -1330,30 +1286,30 @@
       <c r="F14" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="44" t="n">
+      <c r="G14" s="17" t="n">
         <v>46482</v>
       </c>
       <c r="H14" s="14">
         <f>ROUNDUP(E14*IF(D14="Profundo",Premissas!$B$4,Premissas!$B$5)/F14,0)</f>
         <v/>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="18">
         <f>G14+H14*7</f>
         <v/>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>Livro: AI Engineering (Chip Huyen)</t>
+          <t>Book: AI Engineering (Chip Huyen)</t>
         </is>
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Artigo: Building effective agents (Anthropic)</t>
+          <t>Article: Building effective agents (Anthropic)</t>
         </is>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>Prompt / harness / spec; Python</t>
+          <t>Prompt Engineering / Harness / Spec; Python</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
@@ -1370,7 +1326,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Engenharia de dados e governança</t>
+          <t>Data Engineering and Governance</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -1389,30 +1345,30 @@
       <c r="F15" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="44" t="n">
+      <c r="G15" s="17" t="n">
         <v>46482</v>
       </c>
       <c r="H15" s="14">
         <f>ROUNDUP(E15*IF(D15="Profundo",Premissas!$B$4,Premissas!$B$5)/F15,0)</f>
         <v/>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="18">
         <f>G15+H15*7</f>
         <v/>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>Livro: Fundamentals of Data Engineering (Reis &amp; Housley)</t>
+          <t>Book: Fundamentals of Data Engineering (Reis &amp; Housley)</t>
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Repositório: github.com/DataTalksClub/data-engineering-zoomcamp; Livro: Data Governance: The Definitive Guide (Eryurek et al.)</t>
+          <t>Repository: github.com/DataTalksClub/data-engineering-zoomcamp; Book: Data Governance: The Definitive Guide (Eryurek et al.)</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">
         <is>
-          <t>SQL / modelagem; Python</t>
+          <t>SQL / Data Modeling; Python</t>
         </is>
       </c>
       <c r="M15" s="15" t="inlineStr">
@@ -1429,7 +1385,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Ciência da computação</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1448,30 +1404,30 @@
       <c r="F16" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="44" t="n">
+      <c r="G16" s="17" t="n">
         <v>46482</v>
       </c>
       <c r="H16" s="14">
         <f>ROUNDUP(E16*IF(D16="Profundo",Premissas!$B$4,Premissas!$B$5)/F16,0)</f>
         <v/>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="18">
         <f>G16+H16*7</f>
         <v/>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>Livro: Grokking Algorithms, 2ª ed. (Aditya Bhargava)</t>
+          <t>Book: Grokking Algorithms, 2nd ed. (Aditya Bhargava)</t>
         </is>
       </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Curso: CS50x (Harvard, gratuito)</t>
+          <t>Course: CS50x (Harvard, free)</t>
         </is>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>Lógica de programação</t>
+          <t>Programming Logic</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
@@ -1488,7 +1444,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Engenharia de ML</t>
+          <t>ML Engineering</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -1507,30 +1463,30 @@
       <c r="F17" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="46" t="n">
+      <c r="G17" s="22" t="n">
         <v>46573</v>
       </c>
       <c r="H17" s="19">
         <f>ROUNDUP(E17*IF(D17="Profundo",Premissas!$B$4,Premissas!$B$5)/F17,0)</f>
         <v/>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="23">
         <f>G17+H17*7</f>
         <v/>
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>Livro: Designing Machine Learning Systems (Chip Huyen)</t>
+          <t>Book: Designing Machine Learning Systems (Chip Huyen)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>Repositório: github.com/GokuMohandas/Made-With-ML; Livro: Hands-On Machine Learning (Aurélien Géron)</t>
+          <t>Repository: github.com/GokuMohandas/Made-With-ML; Book: Hands-On Machine Learning (Aurélien Géron)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
-          <t>Matemática; Estatística; EDA</t>
+          <t>Mathematics; Statistics; Advanced EDA</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -1547,7 +1503,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>System design</t>
+          <t>System Design</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -1566,30 +1522,30 @@
       <c r="F18" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="46" t="n">
+      <c r="G18" s="22" t="n">
         <v>46573</v>
       </c>
       <c r="H18" s="19">
         <f>ROUNDUP(E18*IF(D18="Profundo",Premissas!$B$4,Premissas!$B$5)/F18,0)</f>
         <v/>
       </c>
-      <c r="I18" s="47">
+      <c r="I18" s="23">
         <f>G18+H18*7</f>
         <v/>
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>Livro: Designing Data-Intensive Applications (Martin Kleppmann)</t>
+          <t>Book: Designing Data-Intensive Applications (Martin Kleppmann)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
         <is>
-          <t>Repositório: github.com/donnemartin/system-design-primer</t>
+          <t>Repository: github.com/donnemartin/system-design-primer</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>Engenharia de dados; Engenharia de IA</t>
+          <t>Data Engineering; AI Engineering</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -1606,7 +1562,7 @@
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>Inglês</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
@@ -1625,23 +1581,23 @@
       <c r="F19" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="48" t="n">
+      <c r="G19" s="27" t="n">
         <v>46296</v>
       </c>
       <c r="H19" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="I19" s="48" t="n">
+      <c r="I19" s="27" t="n">
         <v>46660</v>
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
-          <t>Livro: English Grammar in Use (Raymond Murphy) — só para os tópicos de gramática</t>
+          <t>Book: English Grammar in Use (Raymond Murphy) — grammar topics only</t>
         </is>
       </c>
       <c r="K19" s="25" t="inlineStr">
         <is>
-          <t>Palestras técnicas (PyData, conferências) e as fontes em inglês das outras capacidades</t>
+          <t>Tech talks (PyData, conferences); The sources of every other capability, all studied in English</t>
         </is>
       </c>
       <c r="L19" s="25" t="inlineStr">
@@ -1651,14 +1607,14 @@
       </c>
       <c r="M19" s="25" t="inlineStr">
         <is>
-          <t>Habilidade, não conceito: 12 marcos mensais (aba Inglês — marcos) + hábito diário no almoço.</t>
+          <t>Habilidade, não conceito: 12 marcos mensais (aba Inglês — marcos) + hábito diário no almoço + todas as capacidades estudadas em inglês (imersão diária).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Fontes: sugestões para quando você ainda não tiver material; troque à vontade. A primeira fonte é a que define a ordem das partes.</t>
+          <t>Fontes: sugestões em inglês (o estudo das capacidades é em inglês); troque à vontade. A primeira fonte é a que define a ordem das partes.</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1729,7 @@
           <t>Início da onda 1</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="31" t="n">
         <v>46296</v>
       </c>
       <c r="C8" s="29" t="inlineStr">
@@ -2118,7 +2074,7 @@
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Projetos / Inglês</t>
+          <t>Projetos / English</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2165,17 @@
       <c r="A4" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="50" t="n">
+      <c r="B4" s="35" t="n">
         <v>46326</v>
       </c>
       <c r="C4" s="29" t="inlineStr">
         <is>
-          <t>Rotina de listening de 30 dias seguidos</t>
+          <t>30-day listening streak</t>
         </is>
       </c>
       <c r="D4" s="29" t="inlineStr">
         <is>
-          <t>Sequência de 30 dias na tarefa diária de listening.</t>
+          <t>30-day streak on the daily Listening task.</t>
         </is>
       </c>
     </row>
@@ -2227,17 +2183,17 @@
       <c r="A5" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="50" t="n">
+      <c r="B5" s="35" t="n">
         <v>46356</v>
       </c>
       <c r="C5" s="29" t="inlineStr">
         <is>
-          <t>Ler a documentação do pandas ("Getting started") sem tradutor</t>
+          <t>Read the pandas "Getting started" docs without a translator</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>Resumir em português, sem consultar tradução, o que cada seção ensina.</t>
+          <t>Summarize, without a translator, what each section teaches.</t>
         </is>
       </c>
     </row>
@@ -2245,17 +2201,17 @@
       <c r="A6" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="50" t="n">
+      <c r="B6" s="35" t="n">
         <v>46387</v>
       </c>
       <c r="C6" s="29" t="inlineStr">
         <is>
-          <t>Assistir a uma palestra técnica de 20 min com legenda em inglês</t>
+          <t>Watch a 20-minute tech talk with English subtitles</t>
         </is>
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>Resumo de 5 frases em inglês do que foi dito.</t>
+          <t>A 5-sentence summary in English of what was said.</t>
         </is>
       </c>
     </row>
@@ -2263,17 +2219,17 @@
       <c r="A7" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="50" t="n">
+      <c r="B7" s="35" t="n">
         <v>46418</v>
       </c>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>Escrever um README em inglês para um projeto seu</t>
+          <t>Write an English README for one of my projects</t>
         </is>
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>README publicado no GitHub, revisado pela IA.</t>
+          <t>README published on GitHub, reviewed by AI.</t>
         </is>
       </c>
     </row>
@@ -2281,17 +2237,17 @@
       <c r="A8" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="50" t="n">
+      <c r="B8" s="35" t="n">
         <v>46446</v>
       </c>
       <c r="C8" s="29" t="inlineStr">
         <is>
-          <t>Ler um capítulo de uma fonte técnica em inglês sem tradutor</t>
+          <t>Explain a whole chapter out loud, in English, right after reading it</t>
         </is>
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>Cartão de revisão do capítulo escrito em inglês.</t>
+          <t>A 3-minute recording without notes.</t>
         </is>
       </c>
     </row>
@@ -2299,17 +2255,17 @@
       <c r="A9" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="50" t="n">
+      <c r="B9" s="35" t="n">
         <v>46477</v>
       </c>
       <c r="C9" s="29" t="inlineStr">
         <is>
-          <t>Palestra técnica de 30 min sem legenda</t>
+          <t>Watch a 30-minute tech talk without subtitles</t>
         </is>
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>Resumo falado de 2 minutos, gravado.</t>
+          <t>A 2-minute spoken summary, recorded.</t>
         </is>
       </c>
     </row>
@@ -2317,17 +2273,17 @@
       <c r="A10" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="50" t="n">
+      <c r="B10" s="35" t="n">
         <v>46507</v>
       </c>
       <c r="C10" s="29" t="inlineStr">
         <is>
-          <t>Explicar um projeto seu em 5 minutos</t>
+          <t>Explain one of my projects in 5 minutes</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>Gravação sem roteiro lido.</t>
+          <t>A recording without reading a script.</t>
         </is>
       </c>
     </row>
@@ -2335,17 +2291,17 @@
       <c r="A11" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="50" t="n">
+      <c r="B11" s="35" t="n">
         <v>46538</v>
       </c>
       <c r="C11" s="29" t="inlineStr">
         <is>
-          <t>Escrever um post técnico de ~500 palavras</t>
+          <t>Write a ~500-word technical post</t>
         </is>
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>Post publicado (LinkedIn, blog ou GitHub).</t>
+          <t>Post published (LinkedIn, blog or GitHub).</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2309,17 @@
       <c r="A12" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="50" t="n">
+      <c r="B12" s="35" t="n">
         <v>46568</v>
       </c>
       <c r="C12" s="29" t="inlineStr">
         <is>
-          <t>Conversa de 20 min por voz com IA sobre um tema técnico</t>
+          <t>Hold a 20-minute voice conversation with AI on a technical topic</t>
         </is>
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>Conversa sem pausas longas nem troca para o português.</t>
+          <t>No long pauses and no switching to Portuguese.</t>
         </is>
       </c>
     </row>
@@ -2371,17 +2327,17 @@
       <c r="A13" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="50" t="n">
+      <c r="B13" s="35" t="n">
         <v>46599</v>
       </c>
       <c r="C13" s="29" t="inlineStr">
         <is>
-          <t>Simular uma reunião com cliente: apresentar uma proposta de projeto de dados</t>
+          <t>Simulate a client meeting: pitch a data project proposal</t>
         </is>
       </c>
       <c r="D13" s="29" t="inlineStr">
         <is>
-          <t>Gravação de 10 minutos.</t>
+          <t>A 10-minute recording.</t>
         </is>
       </c>
     </row>
@@ -2389,17 +2345,17 @@
       <c r="A14" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="50" t="n">
+      <c r="B14" s="35" t="n">
         <v>46630</v>
       </c>
       <c r="C14" s="29" t="inlineStr">
         <is>
-          <t>Participar de uma discussão técnica em inglês</t>
+          <t>Join a technical discussion in English</t>
         </is>
       </c>
       <c r="D14" s="29" t="inlineStr">
         <is>
-          <t>Uma issue ou pull request comentado em repositório público.</t>
+          <t>A comment on an issue or pull request in a public repository.</t>
         </is>
       </c>
     </row>
@@ -2407,17 +2363,17 @@
       <c r="A15" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="50" t="n">
+      <c r="B15" s="35" t="n">
         <v>46660</v>
       </c>
       <c r="C15" s="29" t="inlineStr">
         <is>
-          <t>Apresentar um case completo em inglês</t>
+          <t>Present a full case study in English</t>
         </is>
       </c>
       <c r="D15" s="29" t="inlineStr">
         <is>
-          <t>Apresentação de 10 minutos gravada.</t>
+          <t>A 10-minute recorded presentation.</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2440,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Diagnóstico estatístico de vendas</t>
+          <t>Sales Statistical Diagnosis</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Estatística, SQL, Python</t>
+          <t>Statistics, SQL, Python</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -2497,7 +2453,7 @@
           <t>Relatório com consultas SQL e testes de hipótese (ex.: conversão de orçamentos em vendas por bloco).</t>
         </is>
       </c>
-      <c r="E4" s="51" t="n">
+      <c r="E4" s="36" t="n">
         <v>46387</v>
       </c>
     </row>
@@ -2509,12 +2465,12 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Análise de ruptura de estoque para a diretoria</t>
+          <t>Stockout Analysis for the Board</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>EDA avançada, matemática, visualização, storytelling</t>
+          <t>Advanced EDA, Mathematics, Data Visualization, Data Storytelling</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -2522,7 +2478,7 @@
           <t>EDA completa + apresentação de 10 slides com recomendação.</t>
         </is>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="37" t="n">
         <v>46481</v>
       </c>
     </row>
@@ -2534,12 +2490,12 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Assistente de IA sobre a documentação das bases</t>
+          <t>AI Assistant for the Data Documentation (RAG)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Engenharia de IA, engenharia de dados e governança, prompt</t>
+          <t>AI Engineering, Data Engineering and Governance, Prompt Engineering</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
@@ -2547,7 +2503,7 @@
           <t>App que responde perguntas sobre as bases a partir das descrições (RAG), com rotina de atualização.</t>
         </is>
       </c>
-      <c r="E6" s="53" t="n">
+      <c r="E6" s="38" t="n">
         <v>46572</v>
       </c>
     </row>
@@ -2559,12 +2515,12 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Previsão de demanda ou ruptura em produção</t>
+          <t>Demand or Stockout Forecasting in Production</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Engenharia de ML, system design</t>
+          <t>ML Engineering, System Design</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -2572,7 +2528,7 @@
           <t>Modelo treinado, servido e monitorado, com o desenho da arquitetura.</t>
         </is>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="39" t="n">
         <v>46663</v>
       </c>
     </row>

--- a/planejamento/plano-capacidades.xlsx
+++ b/planejamento/plano-capacidades.xlsx
@@ -827,12 +827,12 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Book: Python for Data Analysis, 3rd ed. (Wes McKinney), free at wesmckinney.com/book</t>
+          <t>Book: Fundamentals of Data Engineering (Reis &amp; Housley)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Repository: github.com/jakevdp/PythonDataScienceHandbook</t>
+          <t>Book: Designing Data-Intensive Applications (Kleppmann); Book: The Data Warehouse Toolkit (Kimball &amp; Ross); Book: A Philosophy of Software Design (Ousterhout); Book: How to Solve It (Pólya); Book: Data Pipelines Pocket Reference (Densmore); Book: Python Data Science Handbook (VanderPlas), free at jakevdp.github.io/PythonDataScienceHandbook; Site: c4model.com; Docs: Mermaid (mermaid.js.org)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Ferramenta de tudo que vem depois; você já usa pandas, aqui fecha lacunas.</t>
+          <t>Guiada por conceitos, não por um livro: a lista de conceitos (campo Foco) manda na ordem e os livros são referências por conceito. Pensar e desenhar antes de pedir código à IA é o que mais multiplica o resto.</t>
         </is>
       </c>
     </row>

--- a/planejamento/plano-capacidades.xlsx
+++ b/planejamento/plano-capacidades.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Rotina semanal" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Inglês — marcos" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Projetos integradores" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Capacidades pessoais" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Capacidades'!$A$4:$M$19</definedName>
@@ -130,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -238,6 +239,15 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1791,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2109,6 +2119,20 @@
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Capacidade semanal estimada: 10 sessões nas noites úteis + 12 no fim de semana = 22 (aba Premissas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Leitura pessoal: 2 sessões no domingo à tarde, a partir de 06/11/2026 (aba Capacidades pessoais). Elas saem das 22 sessões por semana depois que Git termina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Exercício (calistenia) e caminhada de domingo: ficam nas tarefas diárias, com o plano da semana em Exercício físico.</t>
         </is>
       </c>
     </row>
@@ -2542,4 +2566,264 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Capacidades pessoais (leitura com aplicação na vida real)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Azul = valores para você ajustar. 2 sessões por semana, no domingo à tarde. Uma de cada vez; a próxima começa quando a anterior termina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ordem</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Capacidade</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Profundidade</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Partes estimadas</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Sessões por semana</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Início</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Semanas estimadas</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Prazo estimado</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Por que nesta posição</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Prática</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>How to Win Friends and Influence People</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>Pessoal</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>Sólido</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="41" t="n">
+        <v>46332</v>
+      </c>
+      <c r="H5" s="34">
+        <f>ROUNDUP(E5*IF(D5="Profundo",Premissas!$B$4,Premissas!$B$5)/F5,0)</f>
+        <v/>
+      </c>
+      <c r="I5" s="42">
+        <f>G5+H5*7</f>
+        <v/>
+      </c>
+      <c r="J5" s="29" t="inlineStr">
+        <is>
+          <t>Book: How to Win Friends and Influence People (Dale Carnegie), Portuguese edition: Como Fazer Amigos e Influenciar Pessoas</t>
+        </is>
+      </c>
+      <c r="K5" s="29" t="inlineStr">
+        <is>
+          <t>Capítulos curtos e práticos, com retorno imediato no trabalho com clientes e na vida pessoal. Começa quando Git termina e libera 3 sessões por semana.</t>
+        </is>
+      </c>
+      <c r="L5" s="29" t="inlineStr">
+        <is>
+          <t>Um princípio por semana vira um experimento em conversas reais (trabalho, família, clientes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>The 7 Habits of Highly Effective People</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Pessoal</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Sólido</t>
+        </is>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="41" t="n">
+        <v>46419</v>
+      </c>
+      <c r="H6" s="34">
+        <f>ROUNDUP(E6*IF(D6="Profundo",Premissas!$B$4,Premissas!$B$5)/F6,0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="42">
+        <f>G6+H6*7</f>
+        <v/>
+      </c>
+      <c r="J6" s="29" t="inlineStr">
+        <is>
+          <t>Book: The 7 Habits of Highly Effective People (Stephen R. Covey), Portuguese edition: Os 7 Hábitos das Pessoas Altamente Eficazes</t>
+        </is>
+      </c>
+      <c r="K6" s="29" t="inlineStr">
+        <is>
+          <t>É cumulativo (vitória privada, depois pública) e conversa com o projeto de disciplina. Vem depois de Carnegie, que prepara os hábitos 4 a 6.</t>
+        </is>
+      </c>
+      <c r="L6" s="29" t="inlineStr">
+        <is>
+          <t>Um hábito vira uma regra pessoal de 7 dias, anotada no app como tarefa diária.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Mere Christianity</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Pessoal</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Conceitual</t>
+        </is>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="41" t="n">
+        <v>46489</v>
+      </c>
+      <c r="H7" s="34">
+        <f>ROUNDUP(E7*IF(D7="Profundo",Premissas!$B$4,Premissas!$B$5)/F7,0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="42">
+        <f>G7+H7*7</f>
+        <v/>
+      </c>
+      <c r="J7" s="29" t="inlineStr">
+        <is>
+          <t>Book: Mere Christianity (C. S. Lewis), Portuguese edition: Cristianismo Puro e Simples</t>
+        </is>
+      </c>
+      <c r="K7" s="29" t="inlineStr">
+        <is>
+          <t>É o mais longo e o menos urgente; lê-se melhor com calma, aos domingos. Pode ir para o início se for prioridade para você.</t>
+        </is>
+      </c>
+      <c r="L7" s="29" t="inlineStr">
+        <is>
+          <t>Cada parte termina com uma pergunta para refletir ou conversar; sem dados, sem scripts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/planejamento/plano-capacidades.xlsx
+++ b/planejamento/plano-capacidades.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Capacidades pessoais" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Capacidades'!$A$4:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Capacidades'!$A$4:$M$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -331,17 +331,17 @@
     <author>Plano</author>
   </authors>
   <commentList>
-    <comment ref="E19" authorId="0" shapeId="0">
+    <comment ref="E18" authorId="0" shapeId="0">
       <text>
         <t>12 marcos mensais, um por parte.</t>
       </text>
     </comment>
-    <comment ref="F19" authorId="0" shapeId="0">
+    <comment ref="F18" authorId="0" shapeId="0">
       <text>
         <t>1 sessão no fim de semana para o marco; o resto é o hábito diário do almoço.</t>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0">
+    <comment ref="H18" authorId="0" shapeId="0">
       <text>
         <t>Contínua: o ano inteiro, sem fórmula.</t>
       </text>
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Book: Designing Data-Intensive Applications (Kleppmann); Book: The Data Warehouse Toolkit (Kimball &amp; Ross); Book: A Philosophy of Software Design (Ousterhout); Book: How to Solve It (Pólya); Book: Data Pipelines Pocket Reference (Densmore); Book: Python Data Science Handbook (VanderPlas), free at jakevdp.github.io/PythonDataScienceHandbook; Site: c4model.com; Docs: Mermaid (mermaid.js.org)</t>
+          <t>Book: Designing Data-Intensive Applications (Kleppmann); Book: The Data Warehouse Toolkit (Kimball &amp; Ross); Book: A Philosophy of Software Design (Ousterhout); Book: How to Solve It (Pólya); Book: Data Pipelines Pocket Reference (Densmore); Book: Python Data Science Handbook (VanderPlas), free at jakevdp.github.io/PythonDataScienceHandbook; Book: Pro Git, 2nd ed. (Chacon &amp; Straub), free at git-scm.com/book — chapters 1–3 and 10 (the Git track); Site: c4model.com; Docs: Mermaid (mermaid.js.org)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Guiada por conceitos, não por um livro: a lista de conceitos (campo Foco) manda na ordem e os livros são referências por conceito. Pensar e desenhar antes de pedir código à IA é o que mais multiplica o resto.</t>
+          <t>Guiada por conceitos, não por um livro: a lista de conceitos (campo Foco) manda na ordem e os livros são referências. Inclui a trilha de Git (cerca de 8 partes). Pensar e desenhar antes de pedir código à IA é o que mais multiplica o resto.</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>A linguagem dos dados em qualquer empresa cliente.</t>
+          <t>A linguagem dos dados em qualquer empresa cliente. É dona da modelagem de dados (granularidade, chaves, esquema em estrela); as regras de prática vêm do campo Regras de prática.</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Git (Conceptual)</t>
+          <t>Prompt Engineering / Harness / Spec</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Conceitual</t>
+          <t>Sólido</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>46296</v>
+        <v>46332</v>
       </c>
       <c r="H8" s="4">
         <f>ROUNDUP(E8*IF(D8="Profundo",Premissas!$B$4,Premissas!$B$5)/F8,0)</f>
@@ -955,81 +955,81 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Book: Pro Git, 2nd ed. (Chacon &amp; Straub), free at git-scm.com/book — chapters 1–3 and 10</t>
+          <t>Repository: github.com/anthropics/prompt-eng-interactive-tutorial</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Article: Building effective agents (Anthropic); Docs: Anthropic documentation on prompting and agents</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Começa em 06/11/2026</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Curta; base para versionar projetos e montar portfólio.</t>
+          <t>Multiplica o seu método de estudo com IA e já vira serviço.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Prompt Engineering / Harness / Spec</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Mathematics for Data Science</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Profissional</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Sólido</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>46332</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="E9" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>46391</v>
+      </c>
+      <c r="H9" s="9">
         <f>ROUNDUP(E9*IF(D9="Profundo",Premissas!$B$4,Premissas!$B$5)/F9,0)</f>
         <v/>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="13">
         <f>G9+H9*7</f>
         <v/>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Repository: github.com/anthropics/prompt-eng-interactive-tutorial</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Article: Building effective agents (Anthropic); Docs: Anthropic documentation on prompting and agents</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Começa quando Git termina</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Multiplica o seu método de estudo com IA e já vira serviço.</t>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Book: Mathematics for Machine Learning (Deisenroth, Faisal &amp; Ong), free at mml-book.github.io</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Course: Essence of Linear Algebra (3Blue1Brown)</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Statistics for Data Science</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Destrava ML: álgebra linear, cálculo e otimização aplicados.</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Mathematics for Data Science</t>
+          <t>Advanced EDA</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1051,14 +1051,14 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Sólido</t>
+          <t>Profundo</t>
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>46391</v>
@@ -1073,22 +1073,22 @@
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Book: Mathematics for Machine Learning (Deisenroth, Faisal &amp; Ong), free at mml-book.github.io</t>
+          <t>Book: Feature Engineering and Selection (Kuhn &amp; Johnson), free at feat.engineering</t>
         </is>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>Course: Essence of Linear Algebra (3Blue1Brown)</t>
+          <t>Repository: github.com/jakevdp/PythonDataScienceHandbook; My own datasets</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>Statistics for Data Science</t>
+          <t>Statistics; Python for Data Science</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>Destrava ML: álgebra linear, cálculo e otimização aplicados.</t>
+          <t>Onde você gera valor mais rápido para um cliente.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Advanced EDA</t>
+          <t>Data Visualization</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1110,14 +1110,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Profundo</t>
+          <t>Sólido</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>46391</v>
@@ -1132,22 +1132,22 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Book: Feature Engineering and Selection (Kuhn &amp; Johnson), free at feat.engineering</t>
+          <t>Book: Fundamentals of Data Visualization (Claus Wilke), free at clauswilke.com/dataviz</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>Repository: github.com/jakevdp/PythonDataScienceHandbook; My own datasets</t>
+          <t>Docs: matplotlib and seaborn</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>Statistics; Python for Data Science</t>
+          <t>Python for Data Science</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>Onde você gera valor mais rápido para um cliente.</t>
+          <t>Base para comunicar qualquer análise.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>Data Storytelling</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="E12" s="11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>46391</v>
+        <v>46447</v>
       </c>
       <c r="H12" s="9">
         <f>ROUNDUP(E12*IF(D12="Profundo",Premissas!$B$4,Premissas!$B$5)/F12,0)</f>
@@ -1191,81 +1191,81 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Book: Fundamentals of Data Visualization (Claus Wilke), free at clauswilke.com/dataviz</t>
+          <t>Book: Storytelling with Data (Cole Nussbaumer Knaflic)</t>
         </is>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>Docs: matplotlib and seaborn</t>
+          <t>Book: Storytelling with Data: Let's Practice! (Knaflic)</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>Python for Data Science</t>
+          <t>Data Visualization</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>Base para comunicar qualquer análise.</t>
+          <t>Explicar e vender o resultado é metade da consultoria.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Data Storytelling</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>AI Engineering</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Profissional</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Sólido</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>46447</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Profundo</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>46482</v>
+      </c>
+      <c r="H13" s="14">
         <f>ROUNDUP(E13*IF(D13="Profundo",Premissas!$B$4,Premissas!$B$5)/F13,0)</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="18">
         <f>G13+H13*7</f>
         <v/>
       </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>Book: Storytelling with Data (Cole Nussbaumer Knaflic)</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>Book: Storytelling with Data: Let's Practice! (Knaflic)</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>Data Visualization</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>Explicar e vender o resultado é metade da consultoria.</t>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>Book: AI Engineering (Chip Huyen)</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Article: Building effective agents (Anthropic)</t>
+        </is>
+      </c>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>Prompt Engineering / Harness / Spec; Python</t>
+        </is>
+      </c>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t>Aplicações com LLM: o serviço mais demandado agora.</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>AI Engineering</t>
+          <t>Data Engineering and Governance</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Profundo</t>
+          <t>Sólido</t>
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G14" s="17" t="n">
         <v>46482</v>
@@ -1309,22 +1309,22 @@
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>Book: AI Engineering (Chip Huyen)</t>
+          <t>Book: Fundamentals of Data Engineering (Reis &amp; Housley)</t>
         </is>
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Article: Building effective agents (Anthropic)</t>
+          <t>Repository: github.com/DataTalksClub/data-engineering-zoomcamp; Book: Data Governance: The Definitive Guide (Eryurek et al.)</t>
         </is>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>Prompt Engineering / Harness / Spec; Python</t>
+          <t>SQL / Data Modeling; Python</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>Aplicações com LLM: o serviço mais demandado agora.</t>
+          <t>Sem dados confiáveis nenhum projeto de cliente fica de pé.</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Data Engineering and Governance</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -1346,14 +1346,14 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Sólido</t>
+          <t>Conceitual</t>
         </is>
       </c>
       <c r="E15" s="16" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>46482</v>
@@ -1368,81 +1368,81 @@
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>Book: Fundamentals of Data Engineering (Reis &amp; Housley)</t>
+          <t>Book: Grokking Algorithms, 2nd ed. (Aditya Bhargava)</t>
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Repository: github.com/DataTalksClub/data-engineering-zoomcamp; Book: Data Governance: The Definitive Guide (Eryurek et al.)</t>
+          <t>Course: CS50x (Harvard, free)</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">
         <is>
-          <t>SQL / Data Modeling; Python</t>
+          <t>Programming Logic</t>
         </is>
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>Sem dados confiáveis nenhum projeto de cliente fica de pé.</t>
+          <t>Estruturas de dados e complexidade para código que escala.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>ML Engineering</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Profissional</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Conceitual</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>46482</v>
-      </c>
-      <c r="H16" s="14">
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Profundo</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>46573</v>
+      </c>
+      <c r="H16" s="19">
         <f>ROUNDUP(E16*IF(D16="Profundo",Premissas!$B$4,Premissas!$B$5)/F16,0)</f>
         <v/>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="23">
         <f>G16+H16*7</f>
         <v/>
       </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Book: Grokking Algorithms, 2nd ed. (Aditya Bhargava)</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>Course: CS50x (Harvard, free)</t>
-        </is>
-      </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>Programming Logic</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="inlineStr">
-        <is>
-          <t>Estruturas de dados e complexidade para código que escala.</t>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>Book: Designing Machine Learning Systems (Chip Huyen)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>Repository: github.com/GokuMohandas/Made-With-ML; Book: Hands-On Machine Learning (Aurélien Géron)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>Mathematics; Statistics; Advanced EDA</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
+        <is>
+          <t>Modelos em produção, do dado ao monitoramento.</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>ML Engineering</t>
+          <t>System Design</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>Profundo</t>
+          <t>Sólido</t>
         </is>
       </c>
       <c r="E17" s="21" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G17" s="22" t="n">
         <v>46573</v>
@@ -1486,150 +1486,91 @@
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>Book: Designing Machine Learning Systems (Chip Huyen)</t>
+          <t>Book: Designing Data-Intensive Applications (Martin Kleppmann)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>Repository: github.com/GokuMohandas/Made-With-ML; Book: Hands-On Machine Learning (Aurélien Géron)</t>
+          <t>Repository: github.com/donnemartin/system-design-primer</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
-          <t>Mathematics; Statistics; Advanced EDA</t>
+          <t>Data Engineering; AI Engineering</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
         <is>
-          <t>Modelos em produção, do dado ao monitoramento.</t>
+          <t>Desenhar a solução inteira para o cliente.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>System Design</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Contínua</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>Profissional</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Sólido</t>
         </is>
       </c>
-      <c r="E18" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>46573</v>
-      </c>
-      <c r="H18" s="19">
-        <f>ROUNDUP(E18*IF(D18="Profundo",Premissas!$B$4,Premissas!$B$5)/F18,0)</f>
-        <v/>
-      </c>
-      <c r="I18" s="23">
-        <f>G18+H18*7</f>
-        <v/>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>Book: Designing Data-Intensive Applications (Martin Kleppmann)</t>
-        </is>
-      </c>
-      <c r="K18" s="20" t="inlineStr">
-        <is>
-          <t>Repository: github.com/donnemartin/system-design-primer</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>Data Engineering; AI Engineering</t>
-        </is>
-      </c>
-      <c r="M18" s="20" t="inlineStr">
-        <is>
-          <t>Desenhar a solução inteira para o cliente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>Contínua</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>Profissional</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>Sólido</t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n">
+      <c r="E18" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="27" t="n">
+      <c r="G18" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H18" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="I19" s="27" t="n">
+      <c r="I18" s="27" t="n">
         <v>46660</v>
       </c>
-      <c r="J19" s="25" t="inlineStr">
+      <c r="J18" s="25" t="inlineStr">
         <is>
           <t>Book: English Grammar in Use (Raymond Murphy) — grammar topics only</t>
         </is>
       </c>
-      <c r="K19" s="25" t="inlineStr">
+      <c r="K18" s="25" t="inlineStr">
         <is>
           <t>Tech talks (PyData, conferences); The sources of every other capability, all studied in English</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
+      <c r="L18" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M19" s="25" t="inlineStr">
+      <c r="M18" s="25" t="inlineStr">
         <is>
           <t>Habilidade, não conceito: 12 marcos mensais (aba Inglês — marcos) + hábito diário no almoço + todas as capacidades estudadas em inglês (imersão diária).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Fontes: sugestões em inglês (o estudo das capacidades é em inglês); troque à vontade. A primeira fonte é a que define a ordem das partes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M19"/>
+  <autoFilter ref="A4:M18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -1772,7 +1713,7 @@
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
         <is>
-          <t>• Não estude as 15 capacidades em paralelo: 1 profunda + 1 ou 2 sólidas + às vezes 1 curta por vez.</t>
+          <t>• Não estude as 14 capacidades em paralelo: 1 profunda + 1 ou 2 sólidas + às vezes 1 curta por vez.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2066,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Leitura pessoal: 2 sessões no domingo à tarde, a partir de 06/11/2026 (aba Capacidades pessoais). Elas saem das 22 sessões por semana depois que Git termina.</t>
+          <t>Leitura pessoal: 2 sessões no domingo à tarde, a partir de 06/11/2026 (aba Capacidades pessoais). Entram nas 22 sessões por semana; de novembro a 03/12 a carga fica cerca de 1 sessão acima, e isso some quando Programação e SQL terminam.</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2651,7 @@
       </c>
       <c r="K5" s="29" t="inlineStr">
         <is>
-          <t>Capítulos curtos e práticos, com retorno imediato no trabalho com clientes e na vida pessoal. Começa quando Git termina e libera 3 sessões por semana.</t>
+          <t>Capítulos curtos e práticos, com retorno imediato no trabalho com clientes e na vida pessoal. Começa em 06/11/2026.</t>
         </is>
       </c>
       <c r="L5" s="29" t="inlineStr">

--- a/planejamento/plano-capacidades.xlsx
+++ b/planejamento/plano-capacidades.xlsx
@@ -2066,7 +2066,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Leitura pessoal: 2 sessões no domingo à tarde, a partir de 06/11/2026 (aba Capacidades pessoais). Entram nas 22 sessões por semana; de novembro a 03/12 a carga fica cerca de 1 sessão acima, e isso some quando Programação e SQL terminam.</t>
+          <t>Leitura pessoal: 2 sessões por semana, Carnegie no sábado e Lewis no domingo, a partir de 06/11/2026 (aba Capacidades pessoais). Entram nas 22 sessões por semana; de novembro a 03/12 a carga fica cerca de 1 sessão acima, e isso some quando Programação e SQL terminam.</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Azul = valores para você ajustar. 2 sessões por semana, no domingo à tarde. Uma de cada vez; a próxima começa quando a anterior termina.</t>
+          <t>Azul = valores para você ajustar. 1 sessão por semana em cada livro: Carnegie no sábado e Lewis no domingo, juntos. Covey começa quando Lewis termina.</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="41" t="n">
         <v>46332</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="K5" s="29" t="inlineStr">
         <is>
-          <t>Capítulos curtos e práticos, com retorno imediato no trabalho com clientes e na vida pessoal. Começa em 06/11/2026.</t>
+          <t>Roda junto com Mere Christianity, 1 sessão por semana, no sábado. Uma sessão por semana combina com os experimentos de 3 a 7 dias.</t>
         </is>
       </c>
       <c r="L5" s="29" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>The 7 Habits of Highly Effective People</t>
+          <t>Mere Christianity</t>
         </is>
       </c>
       <c r="C6" s="29" t="inlineStr">
@@ -2676,17 +2676,17 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>Sólido</t>
+          <t>Conceitual</t>
         </is>
       </c>
       <c r="E6" s="40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="41" t="n">
-        <v>46419</v>
+        <v>46332</v>
       </c>
       <c r="H6" s="34">
         <f>ROUNDUP(E6*IF(D6="Profundo",Premissas!$B$4,Premissas!$B$5)/F6,0)</f>
@@ -2698,17 +2698,17 @@
       </c>
       <c r="J6" s="29" t="inlineStr">
         <is>
-          <t>Book: The 7 Habits of Highly Effective People (Stephen R. Covey), Portuguese edition: Os 7 Hábitos das Pessoas Altamente Eficazes</t>
+          <t>Book: Mere Christianity (C. S. Lewis), Portuguese edition: Cristianismo Puro e Simples</t>
         </is>
       </c>
       <c r="K6" s="29" t="inlineStr">
         <is>
-          <t>É cumulativo (vitória privada, depois pública) e conversa com o projeto de disciplina. Vem depois de Carnegie, que prepara os hábitos 4 a 6.</t>
+          <t>Roda junto com Carnegie, 1 sessão por semana, no domingo. É um argumento para ler com calma e termina primeiro.</t>
         </is>
       </c>
       <c r="L6" s="29" t="inlineStr">
         <is>
-          <t>Um hábito vira uma regra pessoal de 7 dias, anotada no app como tarefa diária.</t>
+          <t>Cada parte termina com uma pergunta para refletir ou conversar; sem dados, sem scripts.</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Mere Christianity</t>
+          <t>The 7 Habits of Highly Effective People</t>
         </is>
       </c>
       <c r="C7" s="29" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>Conceitual</t>
+          <t>Sólido</t>
         </is>
       </c>
       <c r="E7" s="40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="41" t="n">
-        <v>46489</v>
+        <v>46458</v>
       </c>
       <c r="H7" s="34">
         <f>ROUNDUP(E7*IF(D7="Profundo",Premissas!$B$4,Premissas!$B$5)/F7,0)</f>
@@ -2750,17 +2750,17 @@
       </c>
       <c r="J7" s="29" t="inlineStr">
         <is>
-          <t>Book: Mere Christianity (C. S. Lewis), Portuguese edition: Cristianismo Puro e Simples</t>
+          <t>Book: The 7 Habits of Highly Effective People (Stephen R. Covey), Portuguese edition: Os 7 Hábitos das Pessoas Altamente Eficazes</t>
         </is>
       </c>
       <c r="K7" s="29" t="inlineStr">
         <is>
-          <t>É o mais longo e o menos urgente; lê-se melhor com calma, aos domingos. Pode ir para o início se for prioridade para você.</t>
+          <t>Começa quando Mere Christianity termina, com 1 sessão por semana. Quando Carnegie terminar (23/04/2027), suba para 2 sessões por semana.</t>
         </is>
       </c>
       <c r="L7" s="29" t="inlineStr">
         <is>
-          <t>Cada parte termina com uma pergunta para refletir ou conversar; sem dados, sem scripts.</t>
+          <t>Um hábito vira uma regra pessoal de 7 dias, anotada no app como tarefa diária.</t>
         </is>
       </c>
     </row>
